--- a/Data Files/Backoffce/GeraBlocoBCadastroCorretorData/GeraBlocoBCadastroCorretor.xlsx
+++ b/Data Files/Backoffce/GeraBlocoBCadastroCorretorData/GeraBlocoBCadastroCorretor.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\GeraBlocoBCadastroCorretorData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\GeraBlocoBCadastroCorretorData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{C545B47A-7A43-4592-876C-F4206843A4F1}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDCD7779-5386-462C-AE1B-72408567CDD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="15840" windowWidth="29040" xWindow="20370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="GeraBlocoBCadastroCorretor" r:id="rId1" sheetId="2"/>
+    <sheet name="GeraBlocoBCadastroCorretor" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">GeraBlocoBCadastroCorretor!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">GeraBlocoBCadastroCorretor!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -45,9 +45,6 @@
     <t/>
   </si>
   <si>
-    <t>Processar</t>
-  </si>
-  <si>
     <t>Processado</t>
   </si>
   <si>
@@ -58,8 +55,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -81,8 +77,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -107,12 +110,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -124,37 +121,35 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" borderId="0" fillId="5" fontId="0" numFmtId="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -171,10 +166,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -209,7 +204,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -261,7 +256,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -372,21 +367,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -403,7 +398,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -455,25 +450,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="4" width="16.7109375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="4" width="16.42578125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="4" width="74.85546875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="4" width="60.7109375" collapsed="true"/>
-    <col min="5" max="16384" style="4" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="16.7109375" style="4" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="16.42578125" style="4" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="74.85546875" style="4" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="60.7109375" style="4" customWidth="1" collapsed="1"/>
+    <col min="5" max="16384" width="9.140625" style="4" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -491,261 +486,324 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>4030127</v>
+      <c r="A2" s="7">
+        <v>4034700</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="6"/>
     </row>
-    <row customHeight="1" ht="14.25" r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
-        <v>4030128</v>
+        <v>4034690</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>4030129</v>
+      <c r="A4" s="7">
+        <v>4034689</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" s="6"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>4030130</v>
+      <c r="A5" s="7">
+        <v>4034702</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>4030131</v>
+      <c r="A6" s="7">
+        <v>4034703</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
-        <v>4030132</v>
+        <v>4034704</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>4030133</v>
+      <c r="A8" s="7">
+        <v>4034707</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>4030134</v>
+      <c r="A9" s="7">
+        <v>4034684</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" s="6"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>4030135</v>
+      <c r="A10" s="7">
+        <v>4034685</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>4030136</v>
+      <c r="A11" s="7">
+        <v>4034686</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D11" s="6"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>4030137</v>
+      <c r="A12" s="7">
+        <v>4034687</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>4030138</v>
+      <c r="A13" s="7">
+        <v>4034691</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <v>4030139</v>
+      <c r="A14" s="7">
+        <v>4034688</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>4030140</v>
+      <c r="A15" s="7">
+        <v>4034692</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>4030141</v>
+      <c r="A16" s="7">
+        <v>4034693</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" s="6"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
-        <v>4030142</v>
+      <c r="A17" s="7">
+        <v>4034694</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="6"/>
+      <c r="C17" s="6" t="s">
+        <v>6</v>
+      </c>
       <c r="D17" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <v>4030143</v>
+      <c r="A18" s="7">
+        <v>4034695</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="6" t="s">
+        <v>6</v>
+      </c>
       <c r="D18" s="6"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
-        <v>4030144</v>
+      <c r="A19" s="7">
+        <v>4034696</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="6"/>
+      <c r="C19" s="6" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
-        <v>4030145</v>
+      <c r="A20" s="7">
+        <v>4034697</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="6"/>
+      <c r="C20" s="6" t="s">
+        <v>6</v>
+      </c>
       <c r="D20" s="6"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>4034698</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
+        <v>4034699</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>4034701</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>4034705</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>4034706</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins bottom="0.78740157480314965" footer="0.31496062992125984" header="0.31496062992125984" left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
+  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></oddFooter>
-    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></evenFooter>
-    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></firstFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</oddFooter>
+    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</evenFooter>
+    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</firstFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/GeraBlocoBCadastroCorretorData/GeraBlocoBCadastroCorretor.xlsx
+++ b/Data Files/Backoffce/GeraBlocoBCadastroCorretorData/GeraBlocoBCadastroCorretor.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\GeraBlocoBCadastroCorretorData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\GeraBlocoBCadastroCorretorData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDCD7779-5386-462C-AE1B-72408567CDD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{97AFB064-2927-4046-A0AD-F250D039D18C}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="11160" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
   </bookViews>
   <sheets>
-    <sheet name="GeraBlocoBCadastroCorretor" sheetId="2" r:id="rId1"/>
+    <sheet name="GeraBlocoBCadastroCorretor" r:id="rId1" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">GeraBlocoBCadastroCorretor!$A$1:$D$1</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">GeraBlocoBCadastroCorretor!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="8">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>Processar</t>
   </si>
   <si>
     <t>Processado</t>
@@ -55,7 +58,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,15 +81,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="4" tint="-0.499984740745262"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -110,6 +107,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -121,35 +124,40 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="9">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -166,10 +174,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -204,7 +212,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -256,7 +264,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -367,21 +375,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -398,7 +406,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -450,25 +458,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" style="4" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="16.42578125" style="4" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="74.85546875" style="4" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="60.7109375" style="4" customWidth="1" collapsed="1"/>
-    <col min="5" max="16384" width="9.140625" style="4" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="4" width="16.7109375" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="4" width="16.42578125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="4" width="74.85546875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="4" width="60.7109375" collapsed="true"/>
+    <col min="5" max="16384" style="4" width="9.140625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -487,25 +495,25 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
-        <v>4034700</v>
+        <v>4034852</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="6"/>
     </row>
-    <row r="3" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>4034690</v>
+    <row customHeight="1" ht="14.25" r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>4034844</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>4</v>
@@ -513,81 +521,81 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
-        <v>4034689</v>
+        <v>4034824</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="6"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
-        <v>4034702</v>
+        <v>4034847</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
-        <v>4034703</v>
+        <v>4034849</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>4034704</v>
+      <c r="A7" s="8">
+        <v>4034846</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
-        <v>4034707</v>
+        <v>4034845</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
-        <v>4034684</v>
+        <v>4034841</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="6"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
-        <v>4034685</v>
+        <v>4034842</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>4</v>
@@ -595,215 +603,88 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
-        <v>4034686</v>
+        <v>4034843</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="6"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
-        <v>4034687</v>
+        <v>4034850</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
-        <v>4034691</v>
+        <v>4034848</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
-        <v>4034688</v>
+        <v>4034851</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
-        <v>4034692</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>4034693</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="6"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
-        <v>4034694</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
-        <v>4034695</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="6"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
-        <v>4034696</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
-        <v>4034697</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="6"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
-        <v>4034698</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
-        <v>4034699</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
-        <v>4034701</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
-        <v>4034705</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
-        <v>4034706</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins bottom="0.78740157480314965" footer="0.31496062992125984" header="0.31496062992125984" left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</oddFooter>
-    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</evenFooter>
-    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</firstFooter>
+    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></oddFooter>
+    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></evenFooter>
+    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></firstFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/GeraBlocoBCadastroCorretorData/GeraBlocoBCadastroCorretor.xlsx
+++ b/Data Files/Backoffce/GeraBlocoBCadastroCorretorData/GeraBlocoBCadastroCorretor.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\GeraBlocoBCadastroCorretorData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{97AFB064-2927-4046-A0AD-F250D039D18C}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5849614A-BC69-4D26-A572-E13761131265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="11160" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="GeraBlocoBCadastroCorretor" r:id="rId1" sheetId="2"/>
+    <sheet name="GeraBlocoBCadastroCorretor" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">GeraBlocoBCadastroCorretor!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">GeraBlocoBCadastroCorretor!$A$1:$C$1</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="4">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -39,26 +39,13 @@
     <t>Codigo</t>
   </si>
   <si>
-    <t>Erro</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>Processar</t>
   </si>
-  <si>
-    <t>Processado</t>
-  </si>
-  <si>
-    <t>Ramos ativados</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -82,7 +69,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -101,18 +88,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -124,40 +99,34 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -174,10 +143,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -212,7 +181,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -264,7 +233,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -375,21 +344,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -406,7 +375,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -458,28 +427,29 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="4" width="16.7109375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="4" width="16.42578125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="4" width="74.85546875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="4" width="60.7109375" collapsed="true"/>
-    <col min="5" max="16384" style="4" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="16.7109375" style="3" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="16.42578125" style="3" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="74.85546875" style="3" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.140625" style="3" collapsed="1"/>
+    <col min="5" max="5" width="9.140625" style="3"/>
+    <col min="6" max="16384" width="9.140625" style="3" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -489,202 +459,215 @@
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <v>4034852</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="6"/>
-    </row>
-    <row customHeight="1" ht="14.25" r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
-        <v>4034844</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>4034824</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="6"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>4034847</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>4034849</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <v>4034846</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>4034845</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>4034841</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>4034842</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>4034843</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>4034850</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>4034848</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>4034851</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>7</v>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>4036371</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>4036373</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>4036401</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>4036402</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>4036375</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>4036403</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>4036381</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>4036368</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>4036377</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>4036376</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>4036385</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>4036384</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>4036382</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>4036379</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>4036367</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>4036374</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>4036369</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>4036400</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>4036370</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>4036378</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>4036383</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:C1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins bottom="0.78740157480314965" footer="0.31496062992125984" header="0.31496062992125984" left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
+  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></oddFooter>
-    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></evenFooter>
-    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></firstFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</oddFooter>
+    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</evenFooter>
+    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</firstFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/GeraBlocoBCadastroCorretorData/GeraBlocoBCadastroCorretor.xlsx
+++ b/Data Files/Backoffce/GeraBlocoBCadastroCorretorData/GeraBlocoBCadastroCorretor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\GeraBlocoBCadastroCorretorData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5849614A-BC69-4D26-A572-E13761131265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168E18A7-2B19-4494-B176-27CA95DCB646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GeraBlocoBCadastroCorretor" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="4">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -101,12 +101,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -115,12 +112,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -438,194 +436,424 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" style="3" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="16.42578125" style="3" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="74.85546875" style="3" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.140625" style="3" collapsed="1"/>
-    <col min="5" max="5" width="9.140625" style="3"/>
-    <col min="6" max="16384" width="9.140625" style="3" collapsed="1"/>
+    <col min="1" max="1" width="16.6640625" style="2" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="16.44140625" style="2" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="74.88671875" style="8" customWidth="1" collapsed="1"/>
+    <col min="4" max="5" width="9.109375" style="2" collapsed="1"/>
+    <col min="6" max="6" width="43.33203125" style="2" customWidth="1" collapsed="1"/>
+    <col min="7" max="16384" width="9.109375" style="2" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <v>4036371</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="5"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
-        <v>4036373</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>4036401</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>4036402</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>4036375</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>4036403</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>4036381</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
-        <v>4036368</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>4036377</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>4036376</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>4036385</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <v>4036384</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>4036382</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>4036379</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>4036367</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>4036374</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <v>4036369</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
-        <v>4036400</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>4036370</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>4036378</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <v>4036383</v>
-      </c>
-      <c r="B22" s="4" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <v>4038121</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="6"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>4038122</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="7"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>4038123</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>4038124</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>4038125</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>4038126</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>4038127</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>4038128</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>4038129</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>4038130</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>4038133</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>4038134</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>4038135</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>4038136</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>4038137</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>4038138</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>4038139</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>4038143</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>4038144</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>4038145</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>4038146</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>4038147</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>4038148</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>4038149</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>4038150</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>4038151</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>4038152</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>4038153</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>4038154</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>4038155</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>4038157</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>4038158</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>4038159</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>4038160</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
+        <v>4038161</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>4038162</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>4038163</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>4038164</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>4038165</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>4038166</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>4038167</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>4038168</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>4038169</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>4038170</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>4038171</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>4038172</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>4038173</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>4038174</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -643,31 +871,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>